--- a/livrables/temps_scenario_1.xlsx
+++ b/livrables/temps_scenario_1.xlsx
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D4" t="n">
         <v>38</v>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D9" t="n">
         <v>38</v>
@@ -821,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>97.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="G9" t="n">
         <v>6</v>
@@ -830,13 +830,13 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>141.4</v>
+        <v>141.2</v>
       </c>
       <c r="J9" t="n">
-        <v>133.8</v>
+        <v>133.6</v>
       </c>
       <c r="K9" t="n">
-        <v>149</v>
+        <v>148.8</v>
       </c>
       <c r="L9" t="n">
         <v>202.5</v>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D14" t="n">
         <v>38</v>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>90.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>6</v>
@@ -1040,13 +1040,13 @@
         <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>134.2</v>
+        <v>134.1</v>
       </c>
       <c r="J14" t="n">
-        <v>126.6</v>
+        <v>126.5</v>
       </c>
       <c r="K14" t="n">
-        <v>141.8</v>
+        <v>141.7</v>
       </c>
       <c r="L14" t="n">
         <v>202.5</v>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D19" t="n">
         <v>23.5</v>
@@ -1256,7 +1256,7 @@
         <v>106.2</v>
       </c>
       <c r="K19" t="n">
-        <v>117.7</v>
+        <v>117.6</v>
       </c>
       <c r="L19" t="n">
         <v>122</v>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D24" t="n">
         <v>23.5</v>
@@ -1451,7 +1451,7 @@
         <v>5.1</v>
       </c>
       <c r="F24" t="n">
-        <v>65.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="G24" t="n">
         <v>6</v>
@@ -1463,7 +1463,7 @@
         <v>99.7</v>
       </c>
       <c r="J24" t="n">
-        <v>94</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K24" t="n">
         <v>105.4</v>
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D29" t="n">
         <v>23.5</v>
@@ -1661,7 +1661,7 @@
         <v>5.1</v>
       </c>
       <c r="F29" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="G29" t="n">
         <v>6</v>
@@ -1670,10 +1670,10 @@
         <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>93.8</v>
+        <v>93.7</v>
       </c>
       <c r="J29" t="n">
-        <v>88.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="K29" t="n">
         <v>99.5</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D34" t="n">
         <v>18</v>
@@ -1871,7 +1871,7 @@
         <v>5.6</v>
       </c>
       <c r="F34" t="n">
-        <v>182.4</v>
+        <v>182.2</v>
       </c>
       <c r="G34" t="n">
         <v>20</v>
@@ -1880,13 +1880,13 @@
         <v>10</v>
       </c>
       <c r="I34" t="n">
-        <v>226</v>
+        <v>225.9</v>
       </c>
       <c r="J34" t="n">
-        <v>221.3</v>
+        <v>221.1</v>
       </c>
       <c r="K34" t="n">
-        <v>230.7</v>
+        <v>230.6</v>
       </c>
       <c r="L34" t="n">
         <v>275</v>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D39" t="n">
         <v>18</v>
@@ -2081,7 +2081,7 @@
         <v>5.6</v>
       </c>
       <c r="F39" t="n">
-        <v>159.5</v>
+        <v>159.2</v>
       </c>
       <c r="G39" t="n">
         <v>20</v>
@@ -2090,13 +2090,13 @@
         <v>10</v>
       </c>
       <c r="I39" t="n">
-        <v>203.1</v>
+        <v>202.8</v>
       </c>
       <c r="J39" t="n">
-        <v>198.4</v>
+        <v>198.1</v>
       </c>
       <c r="K39" t="n">
-        <v>207.8</v>
+        <v>207.6</v>
       </c>
       <c r="L39" t="n">
         <v>275</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D44" t="n">
         <v>18</v>
@@ -2291,7 +2291,7 @@
         <v>5.6</v>
       </c>
       <c r="F44" t="n">
-        <v>151</v>
+        <v>150.7</v>
       </c>
       <c r="G44" t="n">
         <v>20</v>
@@ -2300,13 +2300,13 @@
         <v>10</v>
       </c>
       <c r="I44" t="n">
-        <v>194.7</v>
+        <v>194.3</v>
       </c>
       <c r="J44" t="n">
-        <v>189.9</v>
+        <v>189.6</v>
       </c>
       <c r="K44" t="n">
-        <v>199.4</v>
+        <v>199</v>
       </c>
       <c r="L44" t="n">
         <v>275</v>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D49" t="n">
         <v>41.5</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>206.4</v>
+        <v>206.1</v>
       </c>
       <c r="G49" t="n">
         <v>18</v>
@@ -2510,13 +2510,13 @@
         <v>9</v>
       </c>
       <c r="I49" t="n">
-        <v>265.9</v>
+        <v>265.6</v>
       </c>
       <c r="J49" t="n">
-        <v>257.6</v>
+        <v>257.3</v>
       </c>
       <c r="K49" t="n">
-        <v>274.2</v>
+        <v>273.9</v>
       </c>
       <c r="L49" t="n">
         <v>318</v>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D54" t="n">
         <v>41.5</v>
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>183.6</v>
+        <v>183.2</v>
       </c>
       <c r="G54" t="n">
         <v>18</v>
@@ -2720,13 +2720,13 @@
         <v>9</v>
       </c>
       <c r="I54" t="n">
-        <v>243.1</v>
+        <v>242.7</v>
       </c>
       <c r="J54" t="n">
-        <v>234.8</v>
+        <v>234.4</v>
       </c>
       <c r="K54" t="n">
-        <v>251.4</v>
+        <v>251</v>
       </c>
       <c r="L54" t="n">
         <v>318</v>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D59" t="n">
         <v>41.5</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>174.9</v>
+        <v>174.4</v>
       </c>
       <c r="G59" t="n">
         <v>18</v>
@@ -2930,13 +2930,13 @@
         <v>9</v>
       </c>
       <c r="I59" t="n">
-        <v>234.4</v>
+        <v>233.9</v>
       </c>
       <c r="J59" t="n">
-        <v>226.1</v>
+        <v>225.6</v>
       </c>
       <c r="K59" t="n">
-        <v>242.7</v>
+        <v>242.2</v>
       </c>
       <c r="L59" t="n">
         <v>318</v>

--- a/livrables/temps_scenario_1.xlsx
+++ b/livrables/temps_scenario_1.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="temps_scenario_1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'temps_scenario_1'!$A$1:$L$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'temps_scenario_1'!$A$1:$L$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D5" t="n">
         <v>38</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="D6" t="n">
         <v>38</v>
@@ -724,11 +724,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>160</v>
+        <v>300</v>
       </c>
       <c r="D7" t="n">
         <v>38</v>
@@ -737,7 +737,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>105.3</v>
+        <v>113.1</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
@@ -746,13 +746,13 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>149.3</v>
+        <v>157.1</v>
       </c>
       <c r="J7" t="n">
-        <v>141.7</v>
+        <v>149.5</v>
       </c>
       <c r="K7" t="n">
-        <v>156.9</v>
+        <v>164.7</v>
       </c>
       <c r="L7" t="n">
         <v>202.5</v>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="D8" t="n">
         <v>38</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>101</v>
+        <v>105.3</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
@@ -788,13 +788,13 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>145</v>
+        <v>149.3</v>
       </c>
       <c r="J8" t="n">
-        <v>137.4</v>
+        <v>141.7</v>
       </c>
       <c r="K8" t="n">
-        <v>152.6</v>
+        <v>156.9</v>
       </c>
       <c r="L8" t="n">
         <v>202.5</v>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D9" t="n">
         <v>38</v>
@@ -821,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>97.2</v>
+        <v>101</v>
       </c>
       <c r="G9" t="n">
         <v>6</v>
@@ -830,13 +830,13 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>141.2</v>
+        <v>145</v>
       </c>
       <c r="J9" t="n">
-        <v>133.6</v>
+        <v>137.4</v>
       </c>
       <c r="K9" t="n">
-        <v>148.8</v>
+        <v>152.6</v>
       </c>
       <c r="L9" t="n">
         <v>202.5</v>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>250</v>
+        <v>201</v>
       </c>
       <c r="D10" t="n">
         <v>38</v>
@@ -863,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>91.90000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="G10" t="n">
         <v>6</v>
@@ -872,13 +872,13 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>135.9</v>
+        <v>141.2</v>
       </c>
       <c r="J10" t="n">
-        <v>128.3</v>
+        <v>133.6</v>
       </c>
       <c r="K10" t="n">
-        <v>143.5</v>
+        <v>148.8</v>
       </c>
       <c r="L10" t="n">
         <v>202.5</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="D11" t="n">
         <v>38</v>
@@ -905,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>90.2</v>
+        <v>94.7</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
@@ -914,13 +914,13 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>134.2</v>
+        <v>138.7</v>
       </c>
       <c r="J11" t="n">
-        <v>126.6</v>
+        <v>131.1</v>
       </c>
       <c r="K11" t="n">
-        <v>141.8</v>
+        <v>146.3</v>
       </c>
       <c r="L11" t="n">
         <v>202.5</v>
@@ -934,11 +934,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="D12" t="n">
         <v>38</v>
@@ -947,7 +947,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>101.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>6</v>
@@ -956,13 +956,13 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>145.5</v>
+        <v>135.9</v>
       </c>
       <c r="J12" t="n">
-        <v>137.9</v>
+        <v>128.3</v>
       </c>
       <c r="K12" t="n">
-        <v>153.1</v>
+        <v>143.5</v>
       </c>
       <c r="L12" t="n">
         <v>202.5</v>
@@ -976,11 +976,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>177</v>
+        <v>300</v>
       </c>
       <c r="D13" t="n">
         <v>38</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>95.2</v>
+        <v>90.2</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
@@ -998,13 +998,13 @@
         <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>139.2</v>
+        <v>134.2</v>
       </c>
       <c r="J13" t="n">
-        <v>131.6</v>
+        <v>126.6</v>
       </c>
       <c r="K13" t="n">
-        <v>146.8</v>
+        <v>141.8</v>
       </c>
       <c r="L13" t="n">
         <v>202.5</v>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="D14" t="n">
         <v>38</v>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>90.09999999999999</v>
+        <v>101.5</v>
       </c>
       <c r="G14" t="n">
         <v>6</v>
@@ -1040,13 +1040,13 @@
         <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>134.1</v>
+        <v>145.5</v>
       </c>
       <c r="J14" t="n">
-        <v>126.5</v>
+        <v>137.9</v>
       </c>
       <c r="K14" t="n">
-        <v>141.7</v>
+        <v>153.1</v>
       </c>
       <c r="L14" t="n">
         <v>202.5</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>250</v>
+        <v>177</v>
       </c>
       <c r="D15" t="n">
         <v>38</v>
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>83.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="G15" t="n">
         <v>6</v>
@@ -1082,13 +1082,13 @@
         <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>127.9</v>
+        <v>139.2</v>
       </c>
       <c r="J15" t="n">
-        <v>120.3</v>
+        <v>131.6</v>
       </c>
       <c r="K15" t="n">
-        <v>135.5</v>
+        <v>146.8</v>
       </c>
       <c r="L15" t="n">
         <v>202.5</v>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="D16" t="n">
         <v>38</v>
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>81.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>6</v>
@@ -1124,13 +1124,13 @@
         <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>125.5</v>
+        <v>134.1</v>
       </c>
       <c r="J16" t="n">
-        <v>117.9</v>
+        <v>126.5</v>
       </c>
       <c r="K16" t="n">
-        <v>133.1</v>
+        <v>141.7</v>
       </c>
       <c r="L16" t="n">
         <v>202.5</v>
@@ -1139,25 +1139,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MTL-Ott</t>
+          <t>MTL-QC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>160</v>
+        <v>241</v>
       </c>
       <c r="D17" t="n">
-        <v>23.5</v>
+        <v>38</v>
       </c>
       <c r="E17" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>79.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="G17" t="n">
         <v>6</v>
@@ -1166,40 +1166,40 @@
         <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>114.2</v>
+        <v>130.5</v>
       </c>
       <c r="J17" t="n">
-        <v>108.5</v>
+        <v>122.9</v>
       </c>
       <c r="K17" t="n">
-        <v>120</v>
+        <v>138.1</v>
       </c>
       <c r="L17" t="n">
-        <v>122</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MTL-Ott</t>
+          <t>MTL-QC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>177</v>
+        <v>250</v>
       </c>
       <c r="D18" t="n">
-        <v>23.5</v>
+        <v>38</v>
       </c>
       <c r="E18" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>78.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>6</v>
@@ -1208,40 +1208,40 @@
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>113</v>
+        <v>127.9</v>
       </c>
       <c r="J18" t="n">
-        <v>107.2</v>
+        <v>120.3</v>
       </c>
       <c r="K18" t="n">
-        <v>118.7</v>
+        <v>135.5</v>
       </c>
       <c r="L18" t="n">
-        <v>122</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MTL-Ott</t>
+          <t>MTL-QC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="D19" t="n">
-        <v>23.5</v>
+        <v>38</v>
       </c>
       <c r="E19" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>77.3</v>
+        <v>81.5</v>
       </c>
       <c r="G19" t="n">
         <v>6</v>
@@ -1250,16 +1250,16 @@
         <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>111.9</v>
+        <v>125.5</v>
       </c>
       <c r="J19" t="n">
-        <v>106.2</v>
+        <v>117.9</v>
       </c>
       <c r="K19" t="n">
-        <v>117.6</v>
+        <v>133.1</v>
       </c>
       <c r="L19" t="n">
-        <v>122</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="20">
@@ -1274,16 +1274,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="D20" t="n">
         <v>23.5</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="F20" t="n">
-        <v>76.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>6</v>
@@ -1292,13 +1292,13 @@
         <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>111.3</v>
+        <v>114.2</v>
       </c>
       <c r="J20" t="n">
-        <v>105.6</v>
+        <v>108.5</v>
       </c>
       <c r="K20" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L20" t="n">
         <v>122</v>
@@ -1316,16 +1316,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>300</v>
+        <v>177</v>
       </c>
       <c r="D21" t="n">
         <v>23.5</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="F21" t="n">
-        <v>76.7</v>
+        <v>78.3</v>
       </c>
       <c r="G21" t="n">
         <v>6</v>
@@ -1334,13 +1334,13 @@
         <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>111.2</v>
+        <v>113</v>
       </c>
       <c r="J21" t="n">
-        <v>105.5</v>
+        <v>107.2</v>
       </c>
       <c r="K21" t="n">
-        <v>116.9</v>
+        <v>118.7</v>
       </c>
       <c r="L21" t="n">
         <v>122</v>
@@ -1354,20 +1354,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="D22" t="n">
         <v>23.5</v>
       </c>
       <c r="E22" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="F22" t="n">
-        <v>68.2</v>
+        <v>77.3</v>
       </c>
       <c r="G22" t="n">
         <v>6</v>
@@ -1376,13 +1376,13 @@
         <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>103</v>
+        <v>111.9</v>
       </c>
       <c r="J22" t="n">
-        <v>97.2</v>
+        <v>106.2</v>
       </c>
       <c r="K22" t="n">
-        <v>108.7</v>
+        <v>117.6</v>
       </c>
       <c r="L22" t="n">
         <v>122</v>
@@ -1396,20 +1396,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>177</v>
+        <v>241</v>
       </c>
       <c r="D23" t="n">
         <v>23.5</v>
       </c>
       <c r="E23" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>66.5</v>
+        <v>76.7</v>
       </c>
       <c r="G23" t="n">
         <v>6</v>
@@ -1418,13 +1418,13 @@
         <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>101.2</v>
+        <v>111.3</v>
       </c>
       <c r="J23" t="n">
-        <v>95.5</v>
+        <v>105.6</v>
       </c>
       <c r="K23" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="L23" t="n">
         <v>122</v>
@@ -1438,20 +1438,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>201</v>
+        <v>250</v>
       </c>
       <c r="D24" t="n">
         <v>23.5</v>
       </c>
       <c r="E24" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>65</v>
+        <v>76.7</v>
       </c>
       <c r="G24" t="n">
         <v>6</v>
@@ -1460,13 +1460,13 @@
         <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>99.7</v>
+        <v>111.3</v>
       </c>
       <c r="J24" t="n">
-        <v>93.90000000000001</v>
+        <v>105.6</v>
       </c>
       <c r="K24" t="n">
-        <v>105.4</v>
+        <v>117</v>
       </c>
       <c r="L24" t="n">
         <v>122</v>
@@ -1480,11 +1480,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="D25" t="n">
         <v>23.5</v>
@@ -1493,7 +1493,7 @@
         <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>62.6</v>
+        <v>76.7</v>
       </c>
       <c r="G25" t="n">
         <v>6</v>
@@ -1502,13 +1502,13 @@
         <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>97.09999999999999</v>
+        <v>111.2</v>
       </c>
       <c r="J25" t="n">
-        <v>91.40000000000001</v>
+        <v>105.5</v>
       </c>
       <c r="K25" t="n">
-        <v>102.8</v>
+        <v>116.9</v>
       </c>
       <c r="L25" t="n">
         <v>122</v>
@@ -1526,16 +1526,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="D26" t="n">
         <v>23.5</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="F26" t="n">
-        <v>61.6</v>
+        <v>68.2</v>
       </c>
       <c r="G26" t="n">
         <v>6</v>
@@ -1544,13 +1544,13 @@
         <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>96.09999999999999</v>
+        <v>103</v>
       </c>
       <c r="J26" t="n">
-        <v>90.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="K26" t="n">
-        <v>101.8</v>
+        <v>108.7</v>
       </c>
       <c r="L26" t="n">
         <v>122</v>
@@ -1564,20 +1564,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="D27" t="n">
         <v>23.5</v>
       </c>
       <c r="E27" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="F27" t="n">
-        <v>66.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="G27" t="n">
         <v>6</v>
@@ -1589,10 +1589,10 @@
         <v>101.2</v>
       </c>
       <c r="J27" t="n">
-        <v>95.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="K27" t="n">
-        <v>106.9</v>
+        <v>107</v>
       </c>
       <c r="L27" t="n">
         <v>122</v>
@@ -1606,20 +1606,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="D28" t="n">
         <v>23.5</v>
       </c>
       <c r="E28" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="F28" t="n">
-        <v>62.2</v>
+        <v>65</v>
       </c>
       <c r="G28" t="n">
         <v>6</v>
@@ -1628,13 +1628,13 @@
         <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>96.90000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="J28" t="n">
-        <v>91.2</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>102.6</v>
+        <v>105.4</v>
       </c>
       <c r="L28" t="n">
         <v>122</v>
@@ -1648,20 +1648,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>201</v>
+        <v>241</v>
       </c>
       <c r="D29" t="n">
         <v>23.5</v>
       </c>
       <c r="E29" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>59.1</v>
+        <v>63.8</v>
       </c>
       <c r="G29" t="n">
         <v>6</v>
@@ -1670,13 +1670,13 @@
         <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>93.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>88</v>
+        <v>92.7</v>
       </c>
       <c r="K29" t="n">
-        <v>99.5</v>
+        <v>104.1</v>
       </c>
       <c r="L29" t="n">
         <v>122</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1703,7 +1703,7 @@
         <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>56.4</v>
+        <v>62.6</v>
       </c>
       <c r="G30" t="n">
         <v>6</v>
@@ -1712,13 +1712,13 @@
         <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>90.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>85.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>96.59999999999999</v>
+        <v>102.8</v>
       </c>
       <c r="L30" t="n">
         <v>122</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1745,7 +1745,7 @@
         <v>5</v>
       </c>
       <c r="F31" t="n">
-        <v>55.3</v>
+        <v>61.6</v>
       </c>
       <c r="G31" t="n">
         <v>6</v>
@@ -1754,13 +1754,13 @@
         <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>89.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>84.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>95.5</v>
+        <v>101.8</v>
       </c>
       <c r="L31" t="n">
         <v>122</v>
@@ -1769,253 +1769,253 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>160</v>
       </c>
       <c r="D32" t="n">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="E32" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="F32" t="n">
-        <v>193.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H32" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
-        <v>237.2</v>
+        <v>101.2</v>
       </c>
       <c r="J32" t="n">
-        <v>232.4</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>241.9</v>
+        <v>106.9</v>
       </c>
       <c r="L32" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>177</v>
       </c>
       <c r="D33" t="n">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="E33" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="F33" t="n">
-        <v>187.4</v>
+        <v>62.2</v>
       </c>
       <c r="G33" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H33" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>231</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>226.3</v>
+        <v>91.2</v>
       </c>
       <c r="K33" t="n">
-        <v>235.8</v>
+        <v>102.6</v>
       </c>
       <c r="L33" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>201</v>
       </c>
       <c r="D34" t="n">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="E34" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="F34" t="n">
-        <v>182.2</v>
+        <v>59.1</v>
       </c>
       <c r="G34" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>225.9</v>
+        <v>93.7</v>
       </c>
       <c r="J34" t="n">
-        <v>221.1</v>
+        <v>88</v>
       </c>
       <c r="K34" t="n">
-        <v>230.6</v>
+        <v>99.5</v>
       </c>
       <c r="L34" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D35" t="n">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="E35" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="F35" t="n">
-        <v>178.8</v>
+        <v>57.7</v>
       </c>
       <c r="G35" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H35" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>222.4</v>
+        <v>92.2</v>
       </c>
       <c r="J35" t="n">
-        <v>217.7</v>
+        <v>86.5</v>
       </c>
       <c r="K35" t="n">
-        <v>227.1</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="D36" t="n">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="E36" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="F36" t="n">
-        <v>178.7</v>
+        <v>56.4</v>
       </c>
       <c r="G36" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H36" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>222.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>217.6</v>
+        <v>85.2</v>
       </c>
       <c r="K36" t="n">
-        <v>227</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>160</v>
+        <v>300</v>
       </c>
       <c r="D37" t="n">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="E37" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="F37" t="n">
-        <v>176.9</v>
+        <v>55.3</v>
       </c>
       <c r="G37" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H37" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>220.6</v>
+        <v>89.8</v>
       </c>
       <c r="J37" t="n">
-        <v>215.8</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>225.3</v>
+        <v>95.5</v>
       </c>
       <c r="L37" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38">
@@ -2026,11 +2026,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="D38" t="n">
         <v>18</v>
@@ -2039,7 +2039,7 @@
         <v>5.7</v>
       </c>
       <c r="F38" t="n">
-        <v>167.6</v>
+        <v>193.5</v>
       </c>
       <c r="G38" t="n">
         <v>20</v>
@@ -2048,13 +2048,13 @@
         <v>10</v>
       </c>
       <c r="I38" t="n">
-        <v>211.2</v>
+        <v>237.2</v>
       </c>
       <c r="J38" t="n">
-        <v>206.5</v>
+        <v>232.4</v>
       </c>
       <c r="K38" t="n">
-        <v>216</v>
+        <v>241.9</v>
       </c>
       <c r="L38" t="n">
         <v>275</v>
@@ -2068,20 +2068,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D39" t="n">
         <v>18</v>
       </c>
       <c r="E39" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="F39" t="n">
-        <v>159.2</v>
+        <v>187.4</v>
       </c>
       <c r="G39" t="n">
         <v>20</v>
@@ -2090,13 +2090,13 @@
         <v>10</v>
       </c>
       <c r="I39" t="n">
-        <v>202.8</v>
+        <v>231</v>
       </c>
       <c r="J39" t="n">
-        <v>198.1</v>
+        <v>226.3</v>
       </c>
       <c r="K39" t="n">
-        <v>207.6</v>
+        <v>235.8</v>
       </c>
       <c r="L39" t="n">
         <v>275</v>
@@ -2110,11 +2110,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>250</v>
+        <v>201</v>
       </c>
       <c r="D40" t="n">
         <v>18</v>
@@ -2123,7 +2123,7 @@
         <v>5.6</v>
       </c>
       <c r="F40" t="n">
-        <v>148.2</v>
+        <v>182.2</v>
       </c>
       <c r="G40" t="n">
         <v>20</v>
@@ -2132,13 +2132,13 @@
         <v>10</v>
       </c>
       <c r="I40" t="n">
-        <v>191.8</v>
+        <v>225.9</v>
       </c>
       <c r="J40" t="n">
-        <v>187.1</v>
+        <v>221.1</v>
       </c>
       <c r="K40" t="n">
-        <v>196.5</v>
+        <v>230.6</v>
       </c>
       <c r="L40" t="n">
         <v>275</v>
@@ -2152,11 +2152,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="D41" t="n">
         <v>18</v>
@@ -2165,7 +2165,7 @@
         <v>5.6</v>
       </c>
       <c r="F41" t="n">
-        <v>143.9</v>
+        <v>179.1</v>
       </c>
       <c r="G41" t="n">
         <v>20</v>
@@ -2174,13 +2174,13 @@
         <v>10</v>
       </c>
       <c r="I41" t="n">
-        <v>187.4</v>
+        <v>222.6</v>
       </c>
       <c r="J41" t="n">
-        <v>182.7</v>
+        <v>217.9</v>
       </c>
       <c r="K41" t="n">
-        <v>192.1</v>
+        <v>227.4</v>
       </c>
       <c r="L41" t="n">
         <v>275</v>
@@ -2194,20 +2194,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="D42" t="n">
         <v>18</v>
       </c>
       <c r="E42" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="F42" t="n">
-        <v>173</v>
+        <v>178.8</v>
       </c>
       <c r="G42" t="n">
         <v>20</v>
@@ -2216,13 +2216,13 @@
         <v>10</v>
       </c>
       <c r="I42" t="n">
-        <v>216.7</v>
+        <v>222.4</v>
       </c>
       <c r="J42" t="n">
-        <v>212</v>
+        <v>217.7</v>
       </c>
       <c r="K42" t="n">
-        <v>221.5</v>
+        <v>227.1</v>
       </c>
       <c r="L42" t="n">
         <v>275</v>
@@ -2236,20 +2236,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>177</v>
+        <v>300</v>
       </c>
       <c r="D43" t="n">
         <v>18</v>
       </c>
       <c r="E43" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="F43" t="n">
-        <v>161.2</v>
+        <v>178.7</v>
       </c>
       <c r="G43" t="n">
         <v>20</v>
@@ -2258,13 +2258,13 @@
         <v>10</v>
       </c>
       <c r="I43" t="n">
-        <v>204.9</v>
+        <v>222.3</v>
       </c>
       <c r="J43" t="n">
-        <v>200.2</v>
+        <v>217.6</v>
       </c>
       <c r="K43" t="n">
-        <v>209.6</v>
+        <v>227</v>
       </c>
       <c r="L43" t="n">
         <v>275</v>
@@ -2278,20 +2278,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="D44" t="n">
         <v>18</v>
       </c>
       <c r="E44" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="F44" t="n">
-        <v>150.7</v>
+        <v>176.9</v>
       </c>
       <c r="G44" t="n">
         <v>20</v>
@@ -2300,13 +2300,13 @@
         <v>10</v>
       </c>
       <c r="I44" t="n">
-        <v>194.3</v>
+        <v>220.6</v>
       </c>
       <c r="J44" t="n">
-        <v>189.6</v>
+        <v>215.8</v>
       </c>
       <c r="K44" t="n">
-        <v>199</v>
+        <v>225.3</v>
       </c>
       <c r="L44" t="n">
         <v>275</v>
@@ -2320,20 +2320,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>250</v>
+        <v>177</v>
       </c>
       <c r="D45" t="n">
         <v>18</v>
       </c>
       <c r="E45" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="F45" t="n">
-        <v>137.9</v>
+        <v>167.6</v>
       </c>
       <c r="G45" t="n">
         <v>20</v>
@@ -2342,13 +2342,13 @@
         <v>10</v>
       </c>
       <c r="I45" t="n">
-        <v>181.5</v>
+        <v>211.2</v>
       </c>
       <c r="J45" t="n">
-        <v>176.8</v>
+        <v>206.5</v>
       </c>
       <c r="K45" t="n">
-        <v>186.2</v>
+        <v>216</v>
       </c>
       <c r="L45" t="n">
         <v>275</v>
@@ -2362,11 +2362,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="D46" t="n">
         <v>18</v>
@@ -2375,7 +2375,7 @@
         <v>5.6</v>
       </c>
       <c r="F46" t="n">
-        <v>132.5</v>
+        <v>159.2</v>
       </c>
       <c r="G46" t="n">
         <v>20</v>
@@ -2384,13 +2384,13 @@
         <v>10</v>
       </c>
       <c r="I46" t="n">
-        <v>176</v>
+        <v>202.8</v>
       </c>
       <c r="J46" t="n">
-        <v>171.3</v>
+        <v>198.1</v>
       </c>
       <c r="K46" t="n">
-        <v>180.7</v>
+        <v>207.6</v>
       </c>
       <c r="L46" t="n">
         <v>275</v>
@@ -2399,379 +2399,379 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>160</v>
+        <v>241</v>
       </c>
       <c r="D47" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="F47" t="n">
-        <v>223.8</v>
+        <v>152.7</v>
       </c>
       <c r="G47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I47" t="n">
-        <v>283.3</v>
+        <v>196.3</v>
       </c>
       <c r="J47" t="n">
+        <v>191.6</v>
+      </c>
+      <c r="K47" t="n">
+        <v>201</v>
+      </c>
+      <c r="L47" t="n">
         <v>275</v>
-      </c>
-      <c r="K47" t="n">
-        <v>291.6</v>
-      </c>
-      <c r="L47" t="n">
-        <v>318</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>177</v>
+        <v>250</v>
       </c>
       <c r="D48" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="F48" t="n">
-        <v>214.6</v>
+        <v>148.2</v>
       </c>
       <c r="G48" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I48" t="n">
-        <v>274.1</v>
+        <v>191.8</v>
       </c>
       <c r="J48" t="n">
-        <v>265.8</v>
+        <v>187.1</v>
       </c>
       <c r="K48" t="n">
-        <v>282.4</v>
+        <v>196.5</v>
       </c>
       <c r="L48" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="D49" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="F49" t="n">
-        <v>206.1</v>
+        <v>143.9</v>
       </c>
       <c r="G49" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I49" t="n">
-        <v>265.6</v>
+        <v>187.4</v>
       </c>
       <c r="J49" t="n">
-        <v>257.3</v>
+        <v>182.7</v>
       </c>
       <c r="K49" t="n">
-        <v>273.9</v>
+        <v>192.1</v>
       </c>
       <c r="L49" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="D50" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="F50" t="n">
-        <v>199.5</v>
+        <v>173</v>
       </c>
       <c r="G50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I50" t="n">
-        <v>259</v>
+        <v>216.7</v>
       </c>
       <c r="J50" t="n">
-        <v>250.7</v>
+        <v>212</v>
       </c>
       <c r="K50" t="n">
-        <v>267.3</v>
+        <v>221.5</v>
       </c>
       <c r="L50" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>300</v>
+        <v>177</v>
       </c>
       <c r="D51" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="F51" t="n">
-        <v>199.5</v>
+        <v>161.2</v>
       </c>
       <c r="G51" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I51" t="n">
-        <v>259</v>
+        <v>204.9</v>
       </c>
       <c r="J51" t="n">
-        <v>250.7</v>
+        <v>200.2</v>
       </c>
       <c r="K51" t="n">
-        <v>267.3</v>
+        <v>209.6</v>
       </c>
       <c r="L51" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="D52" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="F52" t="n">
-        <v>207.3</v>
+        <v>150.7</v>
       </c>
       <c r="G52" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I52" t="n">
-        <v>266.8</v>
+        <v>194.3</v>
       </c>
       <c r="J52" t="n">
-        <v>258.5</v>
+        <v>189.6</v>
       </c>
       <c r="K52" t="n">
-        <v>275.1</v>
+        <v>199</v>
       </c>
       <c r="L52" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>177</v>
+        <v>241</v>
       </c>
       <c r="D53" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="F53" t="n">
-        <v>194.9</v>
+        <v>142.3</v>
       </c>
       <c r="G53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I53" t="n">
-        <v>254.4</v>
+        <v>185.8</v>
       </c>
       <c r="J53" t="n">
-        <v>246.1</v>
+        <v>181.1</v>
       </c>
       <c r="K53" t="n">
-        <v>262.7</v>
+        <v>190.6</v>
       </c>
       <c r="L53" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>201</v>
+        <v>250</v>
       </c>
       <c r="D54" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="F54" t="n">
-        <v>183.2</v>
+        <v>137.9</v>
       </c>
       <c r="G54" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I54" t="n">
-        <v>242.7</v>
+        <v>181.5</v>
       </c>
       <c r="J54" t="n">
-        <v>234.4</v>
+        <v>176.8</v>
       </c>
       <c r="K54" t="n">
-        <v>251</v>
+        <v>186.2</v>
       </c>
       <c r="L54" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="D55" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="F55" t="n">
-        <v>167.3</v>
+        <v>132.5</v>
       </c>
       <c r="G55" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I55" t="n">
-        <v>226.8</v>
+        <v>176</v>
       </c>
       <c r="J55" t="n">
-        <v>218.5</v>
+        <v>171.3</v>
       </c>
       <c r="K55" t="n">
-        <v>235.1</v>
+        <v>180.7</v>
       </c>
       <c r="L55" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="56">
@@ -2782,11 +2782,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="D56" t="n">
         <v>41.5</v>
@@ -2795,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>160.1</v>
+        <v>223.8</v>
       </c>
       <c r="G56" t="n">
         <v>18</v>
@@ -2804,13 +2804,13 @@
         <v>9</v>
       </c>
       <c r="I56" t="n">
-        <v>219.6</v>
+        <v>283.3</v>
       </c>
       <c r="J56" t="n">
-        <v>211.3</v>
+        <v>275</v>
       </c>
       <c r="K56" t="n">
-        <v>227.9</v>
+        <v>291.6</v>
       </c>
       <c r="L56" t="n">
         <v>318</v>
@@ -2824,11 +2824,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="D57" t="n">
         <v>41.5</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>203.7</v>
+        <v>214.6</v>
       </c>
       <c r="G57" t="n">
         <v>18</v>
@@ -2846,13 +2846,13 @@
         <v>9</v>
       </c>
       <c r="I57" t="n">
-        <v>263.2</v>
+        <v>274.1</v>
       </c>
       <c r="J57" t="n">
-        <v>254.9</v>
+        <v>265.8</v>
       </c>
       <c r="K57" t="n">
-        <v>271.5</v>
+        <v>282.4</v>
       </c>
       <c r="L57" t="n">
         <v>318</v>
@@ -2866,11 +2866,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="D58" t="n">
         <v>41.5</v>
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>188.6</v>
+        <v>206.1</v>
       </c>
       <c r="G58" t="n">
         <v>18</v>
@@ -2888,13 +2888,13 @@
         <v>9</v>
       </c>
       <c r="I58" t="n">
-        <v>248.1</v>
+        <v>265.6</v>
       </c>
       <c r="J58" t="n">
-        <v>239.8</v>
+        <v>257.3</v>
       </c>
       <c r="K58" t="n">
-        <v>256.4</v>
+        <v>273.9</v>
       </c>
       <c r="L58" t="n">
         <v>318</v>
@@ -2908,11 +2908,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>201</v>
+        <v>241</v>
       </c>
       <c r="D59" t="n">
         <v>41.5</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>174.4</v>
+        <v>199.8</v>
       </c>
       <c r="G59" t="n">
         <v>18</v>
@@ -2930,13 +2930,13 @@
         <v>9</v>
       </c>
       <c r="I59" t="n">
-        <v>233.9</v>
+        <v>259.3</v>
       </c>
       <c r="J59" t="n">
-        <v>225.6</v>
+        <v>251</v>
       </c>
       <c r="K59" t="n">
-        <v>242.2</v>
+        <v>267.6</v>
       </c>
       <c r="L59" t="n">
         <v>318</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>156.9</v>
+        <v>199.5</v>
       </c>
       <c r="G60" t="n">
         <v>18</v>
@@ -2972,13 +2972,13 @@
         <v>9</v>
       </c>
       <c r="I60" t="n">
-        <v>216.4</v>
+        <v>259</v>
       </c>
       <c r="J60" t="n">
-        <v>208.1</v>
+        <v>250.7</v>
       </c>
       <c r="K60" t="n">
-        <v>224.7</v>
+        <v>267.3</v>
       </c>
       <c r="L60" t="n">
         <v>318</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>148.4</v>
+        <v>199.5</v>
       </c>
       <c r="G61" t="n">
         <v>18</v>
@@ -3014,20 +3014,524 @@
         <v>9</v>
       </c>
       <c r="I61" t="n">
-        <v>207.9</v>
+        <v>259</v>
       </c>
       <c r="J61" t="n">
-        <v>199.6</v>
+        <v>250.7</v>
       </c>
       <c r="K61" t="n">
-        <v>216.2</v>
+        <v>267.3</v>
       </c>
       <c r="L61" t="n">
         <v>318</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>160</v>
+      </c>
+      <c r="D62" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>207.3</v>
+      </c>
+      <c r="G62" t="n">
+        <v>18</v>
+      </c>
+      <c r="H62" t="n">
+        <v>9</v>
+      </c>
+      <c r="I62" t="n">
+        <v>266.8</v>
+      </c>
+      <c r="J62" t="n">
+        <v>258.5</v>
+      </c>
+      <c r="K62" t="n">
+        <v>275.1</v>
+      </c>
+      <c r="L62" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>177</v>
+      </c>
+      <c r="D63" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>194.9</v>
+      </c>
+      <c r="G63" t="n">
+        <v>18</v>
+      </c>
+      <c r="H63" t="n">
+        <v>9</v>
+      </c>
+      <c r="I63" t="n">
+        <v>254.4</v>
+      </c>
+      <c r="J63" t="n">
+        <v>246.1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>262.7</v>
+      </c>
+      <c r="L63" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>201</v>
+      </c>
+      <c r="D64" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="G64" t="n">
+        <v>18</v>
+      </c>
+      <c r="H64" t="n">
+        <v>9</v>
+      </c>
+      <c r="I64" t="n">
+        <v>242.7</v>
+      </c>
+      <c r="J64" t="n">
+        <v>234.4</v>
+      </c>
+      <c r="K64" t="n">
+        <v>251</v>
+      </c>
+      <c r="L64" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>241</v>
+      </c>
+      <c r="D65" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>172.7</v>
+      </c>
+      <c r="G65" t="n">
+        <v>18</v>
+      </c>
+      <c r="H65" t="n">
+        <v>9</v>
+      </c>
+      <c r="I65" t="n">
+        <v>232.2</v>
+      </c>
+      <c r="J65" t="n">
+        <v>223.9</v>
+      </c>
+      <c r="K65" t="n">
+        <v>240.5</v>
+      </c>
+      <c r="L65" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>250</v>
+      </c>
+      <c r="D66" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>167.3</v>
+      </c>
+      <c r="G66" t="n">
+        <v>18</v>
+      </c>
+      <c r="H66" t="n">
+        <v>9</v>
+      </c>
+      <c r="I66" t="n">
+        <v>226.8</v>
+      </c>
+      <c r="J66" t="n">
+        <v>218.5</v>
+      </c>
+      <c r="K66" t="n">
+        <v>235.1</v>
+      </c>
+      <c r="L66" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>300</v>
+      </c>
+      <c r="D67" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>160.1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>18</v>
+      </c>
+      <c r="H67" t="n">
+        <v>9</v>
+      </c>
+      <c r="I67" t="n">
+        <v>219.6</v>
+      </c>
+      <c r="J67" t="n">
+        <v>211.3</v>
+      </c>
+      <c r="K67" t="n">
+        <v>227.9</v>
+      </c>
+      <c r="L67" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>160</v>
+      </c>
+      <c r="D68" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>203.7</v>
+      </c>
+      <c r="G68" t="n">
+        <v>18</v>
+      </c>
+      <c r="H68" t="n">
+        <v>9</v>
+      </c>
+      <c r="I68" t="n">
+        <v>263.2</v>
+      </c>
+      <c r="J68" t="n">
+        <v>254.9</v>
+      </c>
+      <c r="K68" t="n">
+        <v>271.5</v>
+      </c>
+      <c r="L68" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>177</v>
+      </c>
+      <c r="D69" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>188.6</v>
+      </c>
+      <c r="G69" t="n">
+        <v>18</v>
+      </c>
+      <c r="H69" t="n">
+        <v>9</v>
+      </c>
+      <c r="I69" t="n">
+        <v>248.1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>239.8</v>
+      </c>
+      <c r="K69" t="n">
+        <v>256.4</v>
+      </c>
+      <c r="L69" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>201</v>
+      </c>
+      <c r="D70" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>174.4</v>
+      </c>
+      <c r="G70" t="n">
+        <v>18</v>
+      </c>
+      <c r="H70" t="n">
+        <v>9</v>
+      </c>
+      <c r="I70" t="n">
+        <v>233.9</v>
+      </c>
+      <c r="J70" t="n">
+        <v>225.6</v>
+      </c>
+      <c r="K70" t="n">
+        <v>242.2</v>
+      </c>
+      <c r="L70" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>241</v>
+      </c>
+      <c r="D71" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>162</v>
+      </c>
+      <c r="G71" t="n">
+        <v>18</v>
+      </c>
+      <c r="H71" t="n">
+        <v>9</v>
+      </c>
+      <c r="I71" t="n">
+        <v>221.5</v>
+      </c>
+      <c r="J71" t="n">
+        <v>213.2</v>
+      </c>
+      <c r="K71" t="n">
+        <v>229.8</v>
+      </c>
+      <c r="L71" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>250</v>
+      </c>
+      <c r="D72" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="G72" t="n">
+        <v>18</v>
+      </c>
+      <c r="H72" t="n">
+        <v>9</v>
+      </c>
+      <c r="I72" t="n">
+        <v>216.4</v>
+      </c>
+      <c r="J72" t="n">
+        <v>208.1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>224.7</v>
+      </c>
+      <c r="L72" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>300</v>
+      </c>
+      <c r="D73" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>148.4</v>
+      </c>
+      <c r="G73" t="n">
+        <v>18</v>
+      </c>
+      <c r="H73" t="n">
+        <v>9</v>
+      </c>
+      <c r="I73" t="n">
+        <v>207.9</v>
+      </c>
+      <c r="J73" t="n">
+        <v>199.6</v>
+      </c>
+      <c r="K73" t="n">
+        <v>216.2</v>
+      </c>
+      <c r="L73" t="n">
+        <v>318</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L61"/>
+  <autoFilter ref="A1:L73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/livrables/temps_scenario_1.xlsx
+++ b/livrables/temps_scenario_1.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="temps_scenario_1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'temps_scenario_1'!$A$1:$L$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'temps_scenario_1'!$A$1:$L$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -518,16 +518,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D2" t="n">
-        <v>38</v>
+        <v>44.8</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>118.6</v>
+        <v>116.7</v>
       </c>
       <c r="G2" t="n">
         <v>6</v>
@@ -536,13 +536,13 @@
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>162.6</v>
+        <v>167.6</v>
       </c>
       <c r="J2" t="n">
-        <v>155</v>
+        <v>158.6</v>
       </c>
       <c r="K2" t="n">
-        <v>170.2</v>
+        <v>176.5</v>
       </c>
       <c r="L2" t="n">
         <v>202.5</v>
@@ -560,16 +560,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="D3" t="n">
-        <v>38</v>
+        <v>44.8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>115.9</v>
+        <v>115</v>
       </c>
       <c r="G3" t="n">
         <v>6</v>
@@ -578,13 +578,13 @@
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>159.9</v>
+        <v>165.9</v>
       </c>
       <c r="J3" t="n">
-        <v>152.3</v>
+        <v>156.9</v>
       </c>
       <c r="K3" t="n">
-        <v>167.5</v>
+        <v>174.8</v>
       </c>
       <c r="L3" t="n">
         <v>202.5</v>
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>44.8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>113.9</v>
+        <v>112.4</v>
       </c>
       <c r="G4" t="n">
         <v>6</v>
@@ -620,13 +620,13 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>157.9</v>
+        <v>163.2</v>
       </c>
       <c r="J4" t="n">
-        <v>150.3</v>
+        <v>154.3</v>
       </c>
       <c r="K4" t="n">
-        <v>165.5</v>
+        <v>172.2</v>
       </c>
       <c r="L4" t="n">
         <v>202.5</v>
@@ -644,16 +644,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="D5" t="n">
-        <v>38</v>
+        <v>44.8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>113.1</v>
+        <v>110.3</v>
       </c>
       <c r="G5" t="n">
         <v>6</v>
@@ -662,13 +662,13 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>157.1</v>
+        <v>161.2</v>
       </c>
       <c r="J5" t="n">
-        <v>149.5</v>
+        <v>152.2</v>
       </c>
       <c r="K5" t="n">
-        <v>164.7</v>
+        <v>170.1</v>
       </c>
       <c r="L5" t="n">
         <v>202.5</v>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D6" t="n">
-        <v>38</v>
+        <v>44.8</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>113.1</v>
+        <v>109.6</v>
       </c>
       <c r="G6" t="n">
         <v>6</v>
@@ -704,13 +704,13 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>157.1</v>
+        <v>160.4</v>
       </c>
       <c r="J6" t="n">
-        <v>149.5</v>
+        <v>151.4</v>
       </c>
       <c r="K6" t="n">
-        <v>164.7</v>
+        <v>169.4</v>
       </c>
       <c r="L6" t="n">
         <v>202.5</v>
@@ -728,16 +728,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="D7" t="n">
-        <v>38</v>
+        <v>44.8</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>113.1</v>
+        <v>109.6</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
@@ -746,13 +746,13 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>157.1</v>
+        <v>160.4</v>
       </c>
       <c r="J7" t="n">
-        <v>149.5</v>
+        <v>151.4</v>
       </c>
       <c r="K7" t="n">
-        <v>164.7</v>
+        <v>169.4</v>
       </c>
       <c r="L7" t="n">
         <v>202.5</v>
@@ -766,20 +766,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>160</v>
+        <v>300</v>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>44.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>105.3</v>
+        <v>109.6</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
@@ -788,13 +788,13 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>149.3</v>
+        <v>160.4</v>
       </c>
       <c r="J8" t="n">
-        <v>141.7</v>
+        <v>151.4</v>
       </c>
       <c r="K8" t="n">
-        <v>156.9</v>
+        <v>169.4</v>
       </c>
       <c r="L8" t="n">
         <v>202.5</v>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>44.8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>101</v>
+        <v>105.1</v>
       </c>
       <c r="G9" t="n">
         <v>6</v>
@@ -830,13 +830,13 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="J9" t="n">
-        <v>137.4</v>
+        <v>147</v>
       </c>
       <c r="K9" t="n">
-        <v>152.6</v>
+        <v>164.9</v>
       </c>
       <c r="L9" t="n">
         <v>202.5</v>
@@ -854,16 +854,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>38</v>
+        <v>44.8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>97.2</v>
+        <v>102.4</v>
       </c>
       <c r="G10" t="n">
         <v>6</v>
@@ -872,13 +872,13 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>141.2</v>
+        <v>153.3</v>
       </c>
       <c r="J10" t="n">
-        <v>133.6</v>
+        <v>144.3</v>
       </c>
       <c r="K10" t="n">
-        <v>148.8</v>
+        <v>162.2</v>
       </c>
       <c r="L10" t="n">
         <v>202.5</v>
@@ -896,16 +896,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>241</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>38</v>
+        <v>44.8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>94.7</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
@@ -914,13 +914,13 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>138.7</v>
+        <v>149</v>
       </c>
       <c r="J11" t="n">
-        <v>131.1</v>
+        <v>140</v>
       </c>
       <c r="K11" t="n">
-        <v>146.3</v>
+        <v>157.9</v>
       </c>
       <c r="L11" t="n">
         <v>202.5</v>
@@ -938,16 +938,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>250</v>
+        <v>201</v>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>44.8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>91.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>6</v>
@@ -956,13 +956,13 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>135.9</v>
+        <v>145.2</v>
       </c>
       <c r="J12" t="n">
-        <v>128.3</v>
+        <v>136.2</v>
       </c>
       <c r="K12" t="n">
-        <v>143.5</v>
+        <v>154.2</v>
       </c>
       <c r="L12" t="n">
         <v>202.5</v>
@@ -980,16 +980,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>44.8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>90.2</v>
+        <v>91.8</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
@@ -998,13 +998,13 @@
         <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>134.2</v>
+        <v>142.6</v>
       </c>
       <c r="J13" t="n">
-        <v>126.6</v>
+        <v>133.7</v>
       </c>
       <c r="K13" t="n">
-        <v>141.8</v>
+        <v>151.6</v>
       </c>
       <c r="L13" t="n">
         <v>202.5</v>
@@ -1018,20 +1018,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>44.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>101.5</v>
+        <v>89</v>
       </c>
       <c r="G14" t="n">
         <v>6</v>
@@ -1040,13 +1040,13 @@
         <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>145.5</v>
+        <v>139.9</v>
       </c>
       <c r="J14" t="n">
-        <v>137.9</v>
+        <v>130.9</v>
       </c>
       <c r="K14" t="n">
-        <v>153.1</v>
+        <v>148.8</v>
       </c>
       <c r="L14" t="n">
         <v>202.5</v>
@@ -1060,20 +1060,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>177</v>
+        <v>300</v>
       </c>
       <c r="D15" t="n">
-        <v>38</v>
+        <v>44.8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>95.2</v>
+        <v>87.3</v>
       </c>
       <c r="G15" t="n">
         <v>6</v>
@@ -1082,13 +1082,13 @@
         <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>139.2</v>
+        <v>138.1</v>
       </c>
       <c r="J15" t="n">
-        <v>131.6</v>
+        <v>129.2</v>
       </c>
       <c r="K15" t="n">
-        <v>146.8</v>
+        <v>147.1</v>
       </c>
       <c r="L15" t="n">
         <v>202.5</v>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>201</v>
+        <v>153</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>44.8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>90.09999999999999</v>
+        <v>102.3</v>
       </c>
       <c r="G16" t="n">
         <v>6</v>
@@ -1124,13 +1124,13 @@
         <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>134.1</v>
+        <v>153.1</v>
       </c>
       <c r="J16" t="n">
-        <v>126.5</v>
+        <v>144.1</v>
       </c>
       <c r="K16" t="n">
-        <v>141.7</v>
+        <v>162.1</v>
       </c>
       <c r="L16" t="n">
         <v>202.5</v>
@@ -1148,16 +1148,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>241</v>
+        <v>160</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>44.8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>86.5</v>
+        <v>99</v>
       </c>
       <c r="G17" t="n">
         <v>6</v>
@@ -1166,13 +1166,13 @@
         <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>130.5</v>
+        <v>149.8</v>
       </c>
       <c r="J17" t="n">
-        <v>122.9</v>
+        <v>140.8</v>
       </c>
       <c r="K17" t="n">
-        <v>138.1</v>
+        <v>158.8</v>
       </c>
       <c r="L17" t="n">
         <v>202.5</v>
@@ -1190,16 +1190,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>250</v>
+        <v>177</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>44.8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>83.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="G18" t="n">
         <v>6</v>
@@ -1208,13 +1208,13 @@
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>127.9</v>
+        <v>143.5</v>
       </c>
       <c r="J18" t="n">
-        <v>120.3</v>
+        <v>134.5</v>
       </c>
       <c r="K18" t="n">
-        <v>135.5</v>
+        <v>152.5</v>
       </c>
       <c r="L18" t="n">
         <v>202.5</v>
@@ -1232,16 +1232,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>44.8</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>81.5</v>
+        <v>87.5</v>
       </c>
       <c r="G19" t="n">
         <v>6</v>
@@ -1250,13 +1250,13 @@
         <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>125.5</v>
+        <v>138.3</v>
       </c>
       <c r="J19" t="n">
-        <v>117.9</v>
+        <v>129.4</v>
       </c>
       <c r="K19" t="n">
-        <v>133.1</v>
+        <v>147.3</v>
       </c>
       <c r="L19" t="n">
         <v>202.5</v>
@@ -1265,25 +1265,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MTL-Ott</t>
+          <t>MTL-QC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>160</v>
+        <v>241</v>
       </c>
       <c r="D20" t="n">
-        <v>23.5</v>
+        <v>44.8</v>
       </c>
       <c r="E20" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>79.40000000000001</v>
+        <v>84</v>
       </c>
       <c r="G20" t="n">
         <v>6</v>
@@ -1292,40 +1292,40 @@
         <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>114.2</v>
+        <v>134.8</v>
       </c>
       <c r="J20" t="n">
-        <v>108.5</v>
+        <v>125.8</v>
       </c>
       <c r="K20" t="n">
-        <v>120</v>
+        <v>143.8</v>
       </c>
       <c r="L20" t="n">
-        <v>122</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MTL-Ott</t>
+          <t>MTL-QC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>177</v>
+        <v>250</v>
       </c>
       <c r="D21" t="n">
-        <v>23.5</v>
+        <v>44.8</v>
       </c>
       <c r="E21" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>78.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>6</v>
@@ -1334,40 +1334,40 @@
         <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>113</v>
+        <v>132.2</v>
       </c>
       <c r="J21" t="n">
-        <v>107.2</v>
+        <v>123.2</v>
       </c>
       <c r="K21" t="n">
-        <v>118.7</v>
+        <v>141.2</v>
       </c>
       <c r="L21" t="n">
-        <v>122</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MTL-Ott</t>
+          <t>MTL-QC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="D22" t="n">
-        <v>23.5</v>
+        <v>44.8</v>
       </c>
       <c r="E22" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>77.3</v>
+        <v>79</v>
       </c>
       <c r="G22" t="n">
         <v>6</v>
@@ -1376,16 +1376,16 @@
         <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>111.9</v>
+        <v>129.9</v>
       </c>
       <c r="J22" t="n">
-        <v>106.2</v>
+        <v>120.9</v>
       </c>
       <c r="K22" t="n">
-        <v>117.6</v>
+        <v>138.8</v>
       </c>
       <c r="L22" t="n">
-        <v>122</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="23">
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>241</v>
+        <v>153</v>
       </c>
       <c r="D23" t="n">
         <v>23.5</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="F23" t="n">
-        <v>76.7</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>6</v>
@@ -1418,13 +1418,13 @@
         <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>111.3</v>
+        <v>114.9</v>
       </c>
       <c r="J23" t="n">
-        <v>105.6</v>
+        <v>109.1</v>
       </c>
       <c r="K23" t="n">
-        <v>117</v>
+        <v>120.7</v>
       </c>
       <c r="L23" t="n">
         <v>122</v>
@@ -1442,16 +1442,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="D24" t="n">
         <v>23.5</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="F24" t="n">
-        <v>76.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>6</v>
@@ -1460,13 +1460,13 @@
         <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>111.3</v>
+        <v>114.2</v>
       </c>
       <c r="J24" t="n">
-        <v>105.6</v>
+        <v>108.5</v>
       </c>
       <c r="K24" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L24" t="n">
         <v>122</v>
@@ -1484,16 +1484,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>300</v>
+        <v>177</v>
       </c>
       <c r="D25" t="n">
         <v>23.5</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="F25" t="n">
-        <v>76.7</v>
+        <v>78.3</v>
       </c>
       <c r="G25" t="n">
         <v>6</v>
@@ -1502,13 +1502,13 @@
         <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>111.2</v>
+        <v>113</v>
       </c>
       <c r="J25" t="n">
-        <v>105.5</v>
+        <v>107.2</v>
       </c>
       <c r="K25" t="n">
-        <v>116.9</v>
+        <v>118.7</v>
       </c>
       <c r="L25" t="n">
         <v>122</v>
@@ -1522,20 +1522,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="D26" t="n">
         <v>23.5</v>
       </c>
       <c r="E26" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="F26" t="n">
-        <v>68.2</v>
+        <v>77.3</v>
       </c>
       <c r="G26" t="n">
         <v>6</v>
@@ -1544,13 +1544,13 @@
         <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>103</v>
+        <v>111.9</v>
       </c>
       <c r="J26" t="n">
-        <v>97.2</v>
+        <v>106.2</v>
       </c>
       <c r="K26" t="n">
-        <v>108.7</v>
+        <v>117.6</v>
       </c>
       <c r="L26" t="n">
         <v>122</v>
@@ -1564,20 +1564,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>177</v>
+        <v>241</v>
       </c>
       <c r="D27" t="n">
         <v>23.5</v>
       </c>
       <c r="E27" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>66.5</v>
+        <v>76.7</v>
       </c>
       <c r="G27" t="n">
         <v>6</v>
@@ -1586,13 +1586,13 @@
         <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>101.2</v>
+        <v>111.3</v>
       </c>
       <c r="J27" t="n">
-        <v>95.5</v>
+        <v>105.6</v>
       </c>
       <c r="K27" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="L27" t="n">
         <v>122</v>
@@ -1606,20 +1606,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>201</v>
+        <v>250</v>
       </c>
       <c r="D28" t="n">
         <v>23.5</v>
       </c>
       <c r="E28" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>65</v>
+        <v>76.7</v>
       </c>
       <c r="G28" t="n">
         <v>6</v>
@@ -1628,13 +1628,13 @@
         <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>99.7</v>
+        <v>111.3</v>
       </c>
       <c r="J28" t="n">
-        <v>93.90000000000001</v>
+        <v>105.6</v>
       </c>
       <c r="K28" t="n">
-        <v>105.4</v>
+        <v>117</v>
       </c>
       <c r="L28" t="n">
         <v>122</v>
@@ -1648,11 +1648,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>241</v>
+        <v>300</v>
       </c>
       <c r="D29" t="n">
         <v>23.5</v>
@@ -1661,7 +1661,7 @@
         <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>63.8</v>
+        <v>76.7</v>
       </c>
       <c r="G29" t="n">
         <v>6</v>
@@ -1670,13 +1670,13 @@
         <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>98.40000000000001</v>
+        <v>111.2</v>
       </c>
       <c r="J29" t="n">
-        <v>92.7</v>
+        <v>105.5</v>
       </c>
       <c r="K29" t="n">
-        <v>104.1</v>
+        <v>116.9</v>
       </c>
       <c r="L29" t="n">
         <v>122</v>
@@ -1694,16 +1694,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>250</v>
+        <v>153</v>
       </c>
       <c r="D30" t="n">
         <v>23.5</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="F30" t="n">
-        <v>62.6</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G30" t="n">
         <v>6</v>
@@ -1712,13 +1712,13 @@
         <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>97.09999999999999</v>
+        <v>104.9</v>
       </c>
       <c r="J30" t="n">
-        <v>91.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>102.8</v>
+        <v>110.7</v>
       </c>
       <c r="L30" t="n">
         <v>122</v>
@@ -1736,16 +1736,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="D31" t="n">
         <v>23.5</v>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="F31" t="n">
-        <v>61.6</v>
+        <v>68.2</v>
       </c>
       <c r="G31" t="n">
         <v>6</v>
@@ -1754,13 +1754,13 @@
         <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>96.09999999999999</v>
+        <v>103</v>
       </c>
       <c r="J31" t="n">
-        <v>90.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="K31" t="n">
-        <v>101.8</v>
+        <v>108.7</v>
       </c>
       <c r="L31" t="n">
         <v>122</v>
@@ -1774,20 +1774,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="D32" t="n">
         <v>23.5</v>
       </c>
       <c r="E32" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="F32" t="n">
-        <v>66.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="G32" t="n">
         <v>6</v>
@@ -1799,10 +1799,10 @@
         <v>101.2</v>
       </c>
       <c r="J32" t="n">
-        <v>95.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="K32" t="n">
-        <v>106.9</v>
+        <v>107</v>
       </c>
       <c r="L32" t="n">
         <v>122</v>
@@ -1816,20 +1816,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="D33" t="n">
         <v>23.5</v>
       </c>
       <c r="E33" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="F33" t="n">
-        <v>62.2</v>
+        <v>65</v>
       </c>
       <c r="G33" t="n">
         <v>6</v>
@@ -1838,13 +1838,13 @@
         <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>96.90000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="J33" t="n">
-        <v>91.2</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>102.6</v>
+        <v>105.4</v>
       </c>
       <c r="L33" t="n">
         <v>122</v>
@@ -1858,20 +1858,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>201</v>
+        <v>241</v>
       </c>
       <c r="D34" t="n">
         <v>23.5</v>
       </c>
       <c r="E34" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="F34" t="n">
-        <v>59.1</v>
+        <v>63.8</v>
       </c>
       <c r="G34" t="n">
         <v>6</v>
@@ -1880,13 +1880,13 @@
         <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>93.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>88</v>
+        <v>92.7</v>
       </c>
       <c r="K34" t="n">
-        <v>99.5</v>
+        <v>104.1</v>
       </c>
       <c r="L34" t="n">
         <v>122</v>
@@ -1900,11 +1900,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="D35" t="n">
         <v>23.5</v>
@@ -1913,7 +1913,7 @@
         <v>5</v>
       </c>
       <c r="F35" t="n">
-        <v>57.7</v>
+        <v>62.6</v>
       </c>
       <c r="G35" t="n">
         <v>6</v>
@@ -1922,13 +1922,13 @@
         <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>92.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>86.5</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>97.90000000000001</v>
+        <v>102.8</v>
       </c>
       <c r="L35" t="n">
         <v>122</v>
@@ -1942,11 +1942,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="D36" t="n">
         <v>23.5</v>
@@ -1955,7 +1955,7 @@
         <v>5</v>
       </c>
       <c r="F36" t="n">
-        <v>56.4</v>
+        <v>61.6</v>
       </c>
       <c r="G36" t="n">
         <v>6</v>
@@ -1964,13 +1964,13 @@
         <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>90.90000000000001</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>85.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>96.59999999999999</v>
+        <v>101.8</v>
       </c>
       <c r="L36" t="n">
         <v>122</v>
@@ -1988,16 +1988,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>300</v>
+        <v>153</v>
       </c>
       <c r="D37" t="n">
         <v>23.5</v>
       </c>
       <c r="E37" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="F37" t="n">
-        <v>55.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G37" t="n">
         <v>6</v>
@@ -2006,13 +2006,13 @@
         <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>89.8</v>
+        <v>103.4</v>
       </c>
       <c r="J37" t="n">
-        <v>84.09999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>95.5</v>
+        <v>109.2</v>
       </c>
       <c r="L37" t="n">
         <v>122</v>
@@ -2021,253 +2021,253 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>160</v>
       </c>
       <c r="D38" t="n">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="E38" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="F38" t="n">
-        <v>193.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H38" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
-        <v>237.2</v>
+        <v>101.2</v>
       </c>
       <c r="J38" t="n">
-        <v>232.4</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>241.9</v>
+        <v>106.9</v>
       </c>
       <c r="L38" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>177</v>
       </c>
       <c r="D39" t="n">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="E39" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="F39" t="n">
-        <v>187.4</v>
+        <v>62.2</v>
       </c>
       <c r="G39" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H39" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>231</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>226.3</v>
+        <v>91.2</v>
       </c>
       <c r="K39" t="n">
-        <v>235.8</v>
+        <v>102.6</v>
       </c>
       <c r="L39" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>201</v>
       </c>
       <c r="D40" t="n">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="E40" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="F40" t="n">
-        <v>182.2</v>
+        <v>59.1</v>
       </c>
       <c r="G40" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I40" t="n">
-        <v>225.9</v>
+        <v>93.7</v>
       </c>
       <c r="J40" t="n">
-        <v>221.1</v>
+        <v>88</v>
       </c>
       <c r="K40" t="n">
-        <v>230.6</v>
+        <v>99.5</v>
       </c>
       <c r="L40" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>241</v>
       </c>
       <c r="D41" t="n">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="E41" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="F41" t="n">
-        <v>179.1</v>
+        <v>57.7</v>
       </c>
       <c r="G41" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H41" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
-        <v>222.6</v>
+        <v>92.2</v>
       </c>
       <c r="J41" t="n">
-        <v>217.9</v>
+        <v>86.5</v>
       </c>
       <c r="K41" t="n">
-        <v>227.4</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>250</v>
       </c>
       <c r="D42" t="n">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="E42" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="F42" t="n">
-        <v>178.8</v>
+        <v>56.4</v>
       </c>
       <c r="G42" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H42" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I42" t="n">
-        <v>222.4</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>217.7</v>
+        <v>85.2</v>
       </c>
       <c r="K42" t="n">
-        <v>227.1</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>300</v>
       </c>
       <c r="D43" t="n">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="E43" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="F43" t="n">
-        <v>178.7</v>
+        <v>55.3</v>
       </c>
       <c r="G43" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H43" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I43" t="n">
-        <v>222.3</v>
+        <v>89.8</v>
       </c>
       <c r="J43" t="n">
-        <v>217.6</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>227</v>
+        <v>95.5</v>
       </c>
       <c r="L43" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44">
@@ -2278,20 +2278,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D44" t="n">
         <v>18</v>
       </c>
       <c r="E44" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="F44" t="n">
-        <v>176.9</v>
+        <v>197.1</v>
       </c>
       <c r="G44" t="n">
         <v>20</v>
@@ -2300,13 +2300,13 @@
         <v>10</v>
       </c>
       <c r="I44" t="n">
-        <v>220.6</v>
+        <v>240.8</v>
       </c>
       <c r="J44" t="n">
-        <v>215.8</v>
+        <v>236.1</v>
       </c>
       <c r="K44" t="n">
-        <v>225.3</v>
+        <v>245.6</v>
       </c>
       <c r="L44" t="n">
         <v>275</v>
@@ -2320,11 +2320,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="D45" t="n">
         <v>18</v>
@@ -2333,7 +2333,7 @@
         <v>5.7</v>
       </c>
       <c r="F45" t="n">
-        <v>167.6</v>
+        <v>193.5</v>
       </c>
       <c r="G45" t="n">
         <v>20</v>
@@ -2342,13 +2342,13 @@
         <v>10</v>
       </c>
       <c r="I45" t="n">
-        <v>211.2</v>
+        <v>237.2</v>
       </c>
       <c r="J45" t="n">
-        <v>206.5</v>
+        <v>232.4</v>
       </c>
       <c r="K45" t="n">
-        <v>216</v>
+        <v>241.9</v>
       </c>
       <c r="L45" t="n">
         <v>275</v>
@@ -2362,20 +2362,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D46" t="n">
         <v>18</v>
       </c>
       <c r="E46" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="F46" t="n">
-        <v>159.2</v>
+        <v>187.4</v>
       </c>
       <c r="G46" t="n">
         <v>20</v>
@@ -2384,13 +2384,13 @@
         <v>10</v>
       </c>
       <c r="I46" t="n">
-        <v>202.8</v>
+        <v>231</v>
       </c>
       <c r="J46" t="n">
-        <v>198.1</v>
+        <v>226.3</v>
       </c>
       <c r="K46" t="n">
-        <v>207.6</v>
+        <v>235.8</v>
       </c>
       <c r="L46" t="n">
         <v>275</v>
@@ -2404,11 +2404,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="D47" t="n">
         <v>18</v>
@@ -2417,7 +2417,7 @@
         <v>5.6</v>
       </c>
       <c r="F47" t="n">
-        <v>152.7</v>
+        <v>182.2</v>
       </c>
       <c r="G47" t="n">
         <v>20</v>
@@ -2426,13 +2426,13 @@
         <v>10</v>
       </c>
       <c r="I47" t="n">
-        <v>196.3</v>
+        <v>225.9</v>
       </c>
       <c r="J47" t="n">
-        <v>191.6</v>
+        <v>221.1</v>
       </c>
       <c r="K47" t="n">
-        <v>201</v>
+        <v>230.6</v>
       </c>
       <c r="L47" t="n">
         <v>275</v>
@@ -2446,11 +2446,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D48" t="n">
         <v>18</v>
@@ -2459,7 +2459,7 @@
         <v>5.6</v>
       </c>
       <c r="F48" t="n">
-        <v>148.2</v>
+        <v>179.1</v>
       </c>
       <c r="G48" t="n">
         <v>20</v>
@@ -2468,13 +2468,13 @@
         <v>10</v>
       </c>
       <c r="I48" t="n">
-        <v>191.8</v>
+        <v>222.6</v>
       </c>
       <c r="J48" t="n">
-        <v>187.1</v>
+        <v>217.9</v>
       </c>
       <c r="K48" t="n">
-        <v>196.5</v>
+        <v>227.4</v>
       </c>
       <c r="L48" t="n">
         <v>275</v>
@@ -2488,11 +2488,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="D49" t="n">
         <v>18</v>
@@ -2501,7 +2501,7 @@
         <v>5.6</v>
       </c>
       <c r="F49" t="n">
-        <v>143.9</v>
+        <v>178.8</v>
       </c>
       <c r="G49" t="n">
         <v>20</v>
@@ -2510,13 +2510,13 @@
         <v>10</v>
       </c>
       <c r="I49" t="n">
-        <v>187.4</v>
+        <v>222.4</v>
       </c>
       <c r="J49" t="n">
-        <v>182.7</v>
+        <v>217.7</v>
       </c>
       <c r="K49" t="n">
-        <v>192.1</v>
+        <v>227.1</v>
       </c>
       <c r="L49" t="n">
         <v>275</v>
@@ -2530,20 +2530,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>160</v>
+        <v>300</v>
       </c>
       <c r="D50" t="n">
         <v>18</v>
       </c>
       <c r="E50" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="F50" t="n">
-        <v>173</v>
+        <v>178.7</v>
       </c>
       <c r="G50" t="n">
         <v>20</v>
@@ -2552,13 +2552,13 @@
         <v>10</v>
       </c>
       <c r="I50" t="n">
-        <v>216.7</v>
+        <v>222.3</v>
       </c>
       <c r="J50" t="n">
-        <v>212</v>
+        <v>217.6</v>
       </c>
       <c r="K50" t="n">
-        <v>221.5</v>
+        <v>227</v>
       </c>
       <c r="L50" t="n">
         <v>275</v>
@@ -2572,20 +2572,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="D51" t="n">
         <v>18</v>
       </c>
       <c r="E51" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="F51" t="n">
-        <v>161.2</v>
+        <v>181.9</v>
       </c>
       <c r="G51" t="n">
         <v>20</v>
@@ -2594,13 +2594,13 @@
         <v>10</v>
       </c>
       <c r="I51" t="n">
-        <v>204.9</v>
+        <v>225.7</v>
       </c>
       <c r="J51" t="n">
-        <v>200.2</v>
+        <v>220.9</v>
       </c>
       <c r="K51" t="n">
-        <v>209.6</v>
+        <v>230.5</v>
       </c>
       <c r="L51" t="n">
         <v>275</v>
@@ -2614,20 +2614,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="D52" t="n">
         <v>18</v>
       </c>
       <c r="E52" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="F52" t="n">
-        <v>150.7</v>
+        <v>176.9</v>
       </c>
       <c r="G52" t="n">
         <v>20</v>
@@ -2636,13 +2636,13 @@
         <v>10</v>
       </c>
       <c r="I52" t="n">
-        <v>194.3</v>
+        <v>220.6</v>
       </c>
       <c r="J52" t="n">
-        <v>189.6</v>
+        <v>215.8</v>
       </c>
       <c r="K52" t="n">
-        <v>199</v>
+        <v>225.3</v>
       </c>
       <c r="L52" t="n">
         <v>275</v>
@@ -2656,20 +2656,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>241</v>
+        <v>177</v>
       </c>
       <c r="D53" t="n">
         <v>18</v>
       </c>
       <c r="E53" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="F53" t="n">
-        <v>142.3</v>
+        <v>167.6</v>
       </c>
       <c r="G53" t="n">
         <v>20</v>
@@ -2678,13 +2678,13 @@
         <v>10</v>
       </c>
       <c r="I53" t="n">
-        <v>185.8</v>
+        <v>211.2</v>
       </c>
       <c r="J53" t="n">
-        <v>181.1</v>
+        <v>206.5</v>
       </c>
       <c r="K53" t="n">
-        <v>190.6</v>
+        <v>216</v>
       </c>
       <c r="L53" t="n">
         <v>275</v>
@@ -2698,11 +2698,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>250</v>
+        <v>201</v>
       </c>
       <c r="D54" t="n">
         <v>18</v>
@@ -2711,7 +2711,7 @@
         <v>5.6</v>
       </c>
       <c r="F54" t="n">
-        <v>137.9</v>
+        <v>159.2</v>
       </c>
       <c r="G54" t="n">
         <v>20</v>
@@ -2720,13 +2720,13 @@
         <v>10</v>
       </c>
       <c r="I54" t="n">
-        <v>181.5</v>
+        <v>202.8</v>
       </c>
       <c r="J54" t="n">
-        <v>176.8</v>
+        <v>198.1</v>
       </c>
       <c r="K54" t="n">
-        <v>186.2</v>
+        <v>207.6</v>
       </c>
       <c r="L54" t="n">
         <v>275</v>
@@ -2740,11 +2740,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="D55" t="n">
         <v>18</v>
@@ -2753,7 +2753,7 @@
         <v>5.6</v>
       </c>
       <c r="F55" t="n">
-        <v>132.5</v>
+        <v>152.7</v>
       </c>
       <c r="G55" t="n">
         <v>20</v>
@@ -2762,13 +2762,13 @@
         <v>10</v>
       </c>
       <c r="I55" t="n">
-        <v>176</v>
+        <v>196.3</v>
       </c>
       <c r="J55" t="n">
-        <v>171.3</v>
+        <v>191.6</v>
       </c>
       <c r="K55" t="n">
-        <v>180.7</v>
+        <v>201</v>
       </c>
       <c r="L55" t="n">
         <v>275</v>
@@ -2777,379 +2777,379 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="D56" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="F56" t="n">
-        <v>223.8</v>
+        <v>148.2</v>
       </c>
       <c r="G56" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I56" t="n">
-        <v>283.3</v>
+        <v>191.8</v>
       </c>
       <c r="J56" t="n">
+        <v>187.1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="L56" t="n">
         <v>275</v>
-      </c>
-      <c r="K56" t="n">
-        <v>291.6</v>
-      </c>
-      <c r="L56" t="n">
-        <v>318</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>177</v>
+        <v>300</v>
       </c>
       <c r="D57" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="F57" t="n">
-        <v>214.6</v>
+        <v>143.9</v>
       </c>
       <c r="G57" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I57" t="n">
-        <v>274.1</v>
+        <v>187.4</v>
       </c>
       <c r="J57" t="n">
-        <v>265.8</v>
+        <v>182.7</v>
       </c>
       <c r="K57" t="n">
-        <v>282.4</v>
+        <v>192.1</v>
       </c>
       <c r="L57" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>201</v>
+        <v>153</v>
       </c>
       <c r="D58" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="F58" t="n">
-        <v>206.1</v>
+        <v>179</v>
       </c>
       <c r="G58" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I58" t="n">
-        <v>265.6</v>
+        <v>222.8</v>
       </c>
       <c r="J58" t="n">
-        <v>257.3</v>
+        <v>218</v>
       </c>
       <c r="K58" t="n">
-        <v>273.9</v>
+        <v>227.5</v>
       </c>
       <c r="L58" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>241</v>
+        <v>160</v>
       </c>
       <c r="D59" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="F59" t="n">
-        <v>199.8</v>
+        <v>173</v>
       </c>
       <c r="G59" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I59" t="n">
-        <v>259.3</v>
+        <v>216.7</v>
       </c>
       <c r="J59" t="n">
-        <v>251</v>
+        <v>212</v>
       </c>
       <c r="K59" t="n">
-        <v>267.6</v>
+        <v>221.5</v>
       </c>
       <c r="L59" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>250</v>
+        <v>177</v>
       </c>
       <c r="D60" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="F60" t="n">
-        <v>199.5</v>
+        <v>161.2</v>
       </c>
       <c r="G60" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I60" t="n">
-        <v>259</v>
+        <v>204.9</v>
       </c>
       <c r="J60" t="n">
-        <v>250.7</v>
+        <v>200.2</v>
       </c>
       <c r="K60" t="n">
-        <v>267.3</v>
+        <v>209.6</v>
       </c>
       <c r="L60" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="D61" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="F61" t="n">
-        <v>199.5</v>
+        <v>150.7</v>
       </c>
       <c r="G61" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I61" t="n">
-        <v>259</v>
+        <v>194.3</v>
       </c>
       <c r="J61" t="n">
-        <v>250.7</v>
+        <v>189.6</v>
       </c>
       <c r="K61" t="n">
-        <v>267.3</v>
+        <v>199</v>
       </c>
       <c r="L61" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>160</v>
+        <v>241</v>
       </c>
       <c r="D62" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="F62" t="n">
-        <v>207.3</v>
+        <v>142.3</v>
       </c>
       <c r="G62" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I62" t="n">
-        <v>266.8</v>
+        <v>185.8</v>
       </c>
       <c r="J62" t="n">
-        <v>258.5</v>
+        <v>181.1</v>
       </c>
       <c r="K62" t="n">
-        <v>275.1</v>
+        <v>190.6</v>
       </c>
       <c r="L62" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>177</v>
+        <v>250</v>
       </c>
       <c r="D63" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="F63" t="n">
-        <v>194.9</v>
+        <v>137.9</v>
       </c>
       <c r="G63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I63" t="n">
-        <v>254.4</v>
+        <v>181.5</v>
       </c>
       <c r="J63" t="n">
-        <v>246.1</v>
+        <v>176.8</v>
       </c>
       <c r="K63" t="n">
-        <v>262.7</v>
+        <v>186.2</v>
       </c>
       <c r="L63" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="D64" t="n">
-        <v>41.5</v>
+        <v>18</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="F64" t="n">
-        <v>183.2</v>
+        <v>132.5</v>
       </c>
       <c r="G64" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I64" t="n">
-        <v>242.7</v>
+        <v>176</v>
       </c>
       <c r="J64" t="n">
-        <v>234.4</v>
+        <v>171.3</v>
       </c>
       <c r="K64" t="n">
-        <v>251</v>
+        <v>180.7</v>
       </c>
       <c r="L64" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="65">
@@ -3160,11 +3160,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>241</v>
+        <v>153</v>
       </c>
       <c r="D65" t="n">
         <v>41.5</v>
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>172.7</v>
+        <v>228.9</v>
       </c>
       <c r="G65" t="n">
         <v>18</v>
@@ -3182,13 +3182,13 @@
         <v>9</v>
       </c>
       <c r="I65" t="n">
-        <v>232.2</v>
+        <v>288.4</v>
       </c>
       <c r="J65" t="n">
-        <v>223.9</v>
+        <v>280.1</v>
       </c>
       <c r="K65" t="n">
-        <v>240.5</v>
+        <v>296.7</v>
       </c>
       <c r="L65" t="n">
         <v>318</v>
@@ -3202,11 +3202,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="D66" t="n">
         <v>41.5</v>
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>167.3</v>
+        <v>223.8</v>
       </c>
       <c r="G66" t="n">
         <v>18</v>
@@ -3224,13 +3224,13 @@
         <v>9</v>
       </c>
       <c r="I66" t="n">
-        <v>226.8</v>
+        <v>283.3</v>
       </c>
       <c r="J66" t="n">
-        <v>218.5</v>
+        <v>275</v>
       </c>
       <c r="K66" t="n">
-        <v>235.1</v>
+        <v>291.6</v>
       </c>
       <c r="L66" t="n">
         <v>318</v>
@@ -3244,11 +3244,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>300</v>
+        <v>177</v>
       </c>
       <c r="D67" t="n">
         <v>41.5</v>
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>160.1</v>
+        <v>214.6</v>
       </c>
       <c r="G67" t="n">
         <v>18</v>
@@ -3266,13 +3266,13 @@
         <v>9</v>
       </c>
       <c r="I67" t="n">
-        <v>219.6</v>
+        <v>274.1</v>
       </c>
       <c r="J67" t="n">
-        <v>211.3</v>
+        <v>265.8</v>
       </c>
       <c r="K67" t="n">
-        <v>227.9</v>
+        <v>282.4</v>
       </c>
       <c r="L67" t="n">
         <v>318</v>
@@ -3286,11 +3286,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="D68" t="n">
         <v>41.5</v>
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>203.7</v>
+        <v>206.1</v>
       </c>
       <c r="G68" t="n">
         <v>18</v>
@@ -3308,13 +3308,13 @@
         <v>9</v>
       </c>
       <c r="I68" t="n">
-        <v>263.2</v>
+        <v>265.6</v>
       </c>
       <c r="J68" t="n">
-        <v>254.9</v>
+        <v>257.3</v>
       </c>
       <c r="K68" t="n">
-        <v>271.5</v>
+        <v>273.9</v>
       </c>
       <c r="L68" t="n">
         <v>318</v>
@@ -3328,11 +3328,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>177</v>
+        <v>241</v>
       </c>
       <c r="D69" t="n">
         <v>41.5</v>
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>188.6</v>
+        <v>199.8</v>
       </c>
       <c r="G69" t="n">
         <v>18</v>
@@ -3350,13 +3350,13 @@
         <v>9</v>
       </c>
       <c r="I69" t="n">
-        <v>248.1</v>
+        <v>259.3</v>
       </c>
       <c r="J69" t="n">
-        <v>239.8</v>
+        <v>251</v>
       </c>
       <c r="K69" t="n">
-        <v>256.4</v>
+        <v>267.6</v>
       </c>
       <c r="L69" t="n">
         <v>318</v>
@@ -3370,11 +3370,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>201</v>
+        <v>250</v>
       </c>
       <c r="D70" t="n">
         <v>41.5</v>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>174.4</v>
+        <v>199.5</v>
       </c>
       <c r="G70" t="n">
         <v>18</v>
@@ -3392,13 +3392,13 @@
         <v>9</v>
       </c>
       <c r="I70" t="n">
-        <v>233.9</v>
+        <v>259</v>
       </c>
       <c r="J70" t="n">
-        <v>225.6</v>
+        <v>250.7</v>
       </c>
       <c r="K70" t="n">
-        <v>242.2</v>
+        <v>267.3</v>
       </c>
       <c r="L70" t="n">
         <v>318</v>
@@ -3412,11 +3412,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>241</v>
+        <v>300</v>
       </c>
       <c r="D71" t="n">
         <v>41.5</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>162</v>
+        <v>199.5</v>
       </c>
       <c r="G71" t="n">
         <v>18</v>
@@ -3434,13 +3434,13 @@
         <v>9</v>
       </c>
       <c r="I71" t="n">
-        <v>221.5</v>
+        <v>259</v>
       </c>
       <c r="J71" t="n">
-        <v>213.2</v>
+        <v>250.7</v>
       </c>
       <c r="K71" t="n">
-        <v>229.8</v>
+        <v>267.3</v>
       </c>
       <c r="L71" t="n">
         <v>318</v>
@@ -3454,11 +3454,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>250</v>
+        <v>153</v>
       </c>
       <c r="D72" t="n">
         <v>41.5</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>156.9</v>
+        <v>213.9</v>
       </c>
       <c r="G72" t="n">
         <v>18</v>
@@ -3476,13 +3476,13 @@
         <v>9</v>
       </c>
       <c r="I72" t="n">
-        <v>216.4</v>
+        <v>273.4</v>
       </c>
       <c r="J72" t="n">
-        <v>208.1</v>
+        <v>265.1</v>
       </c>
       <c r="K72" t="n">
-        <v>224.7</v>
+        <v>281.7</v>
       </c>
       <c r="L72" t="n">
         <v>318</v>
@@ -3496,11 +3496,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="D73" t="n">
         <v>41.5</v>
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>148.4</v>
+        <v>207.3</v>
       </c>
       <c r="G73" t="n">
         <v>18</v>
@@ -3518,20 +3518,524 @@
         <v>9</v>
       </c>
       <c r="I73" t="n">
-        <v>207.9</v>
+        <v>266.8</v>
       </c>
       <c r="J73" t="n">
-        <v>199.6</v>
+        <v>258.5</v>
       </c>
       <c r="K73" t="n">
-        <v>216.2</v>
+        <v>275.1</v>
       </c>
       <c r="L73" t="n">
         <v>318</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>177</v>
+      </c>
+      <c r="D74" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>194.9</v>
+      </c>
+      <c r="G74" t="n">
+        <v>18</v>
+      </c>
+      <c r="H74" t="n">
+        <v>9</v>
+      </c>
+      <c r="I74" t="n">
+        <v>254.4</v>
+      </c>
+      <c r="J74" t="n">
+        <v>246.1</v>
+      </c>
+      <c r="K74" t="n">
+        <v>262.7</v>
+      </c>
+      <c r="L74" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>201</v>
+      </c>
+      <c r="D75" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>18</v>
+      </c>
+      <c r="H75" t="n">
+        <v>9</v>
+      </c>
+      <c r="I75" t="n">
+        <v>242.7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>234.4</v>
+      </c>
+      <c r="K75" t="n">
+        <v>251</v>
+      </c>
+      <c r="L75" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>241</v>
+      </c>
+      <c r="D76" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>172.7</v>
+      </c>
+      <c r="G76" t="n">
+        <v>18</v>
+      </c>
+      <c r="H76" t="n">
+        <v>9</v>
+      </c>
+      <c r="I76" t="n">
+        <v>232.2</v>
+      </c>
+      <c r="J76" t="n">
+        <v>223.9</v>
+      </c>
+      <c r="K76" t="n">
+        <v>240.5</v>
+      </c>
+      <c r="L76" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>250</v>
+      </c>
+      <c r="D77" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>167.3</v>
+      </c>
+      <c r="G77" t="n">
+        <v>18</v>
+      </c>
+      <c r="H77" t="n">
+        <v>9</v>
+      </c>
+      <c r="I77" t="n">
+        <v>226.8</v>
+      </c>
+      <c r="J77" t="n">
+        <v>218.5</v>
+      </c>
+      <c r="K77" t="n">
+        <v>235.1</v>
+      </c>
+      <c r="L77" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>300</v>
+      </c>
+      <c r="D78" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>160.1</v>
+      </c>
+      <c r="G78" t="n">
+        <v>18</v>
+      </c>
+      <c r="H78" t="n">
+        <v>9</v>
+      </c>
+      <c r="I78" t="n">
+        <v>219.6</v>
+      </c>
+      <c r="J78" t="n">
+        <v>211.3</v>
+      </c>
+      <c r="K78" t="n">
+        <v>227.9</v>
+      </c>
+      <c r="L78" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>153</v>
+      </c>
+      <c r="D79" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>211.4</v>
+      </c>
+      <c r="G79" t="n">
+        <v>18</v>
+      </c>
+      <c r="H79" t="n">
+        <v>9</v>
+      </c>
+      <c r="I79" t="n">
+        <v>270.9</v>
+      </c>
+      <c r="J79" t="n">
+        <v>262.6</v>
+      </c>
+      <c r="K79" t="n">
+        <v>279.2</v>
+      </c>
+      <c r="L79" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>160</v>
+      </c>
+      <c r="D80" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>203.7</v>
+      </c>
+      <c r="G80" t="n">
+        <v>18</v>
+      </c>
+      <c r="H80" t="n">
+        <v>9</v>
+      </c>
+      <c r="I80" t="n">
+        <v>263.2</v>
+      </c>
+      <c r="J80" t="n">
+        <v>254.9</v>
+      </c>
+      <c r="K80" t="n">
+        <v>271.5</v>
+      </c>
+      <c r="L80" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>177</v>
+      </c>
+      <c r="D81" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>188.6</v>
+      </c>
+      <c r="G81" t="n">
+        <v>18</v>
+      </c>
+      <c r="H81" t="n">
+        <v>9</v>
+      </c>
+      <c r="I81" t="n">
+        <v>248.1</v>
+      </c>
+      <c r="J81" t="n">
+        <v>239.8</v>
+      </c>
+      <c r="K81" t="n">
+        <v>256.4</v>
+      </c>
+      <c r="L81" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>201</v>
+      </c>
+      <c r="D82" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>174.4</v>
+      </c>
+      <c r="G82" t="n">
+        <v>18</v>
+      </c>
+      <c r="H82" t="n">
+        <v>9</v>
+      </c>
+      <c r="I82" t="n">
+        <v>233.9</v>
+      </c>
+      <c r="J82" t="n">
+        <v>225.6</v>
+      </c>
+      <c r="K82" t="n">
+        <v>242.2</v>
+      </c>
+      <c r="L82" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>241</v>
+      </c>
+      <c r="D83" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>162</v>
+      </c>
+      <c r="G83" t="n">
+        <v>18</v>
+      </c>
+      <c r="H83" t="n">
+        <v>9</v>
+      </c>
+      <c r="I83" t="n">
+        <v>221.5</v>
+      </c>
+      <c r="J83" t="n">
+        <v>213.2</v>
+      </c>
+      <c r="K83" t="n">
+        <v>229.8</v>
+      </c>
+      <c r="L83" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>250</v>
+      </c>
+      <c r="D84" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="G84" t="n">
+        <v>18</v>
+      </c>
+      <c r="H84" t="n">
+        <v>9</v>
+      </c>
+      <c r="I84" t="n">
+        <v>216.4</v>
+      </c>
+      <c r="J84" t="n">
+        <v>208.1</v>
+      </c>
+      <c r="K84" t="n">
+        <v>224.7</v>
+      </c>
+      <c r="L84" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>300</v>
+      </c>
+      <c r="D85" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>148.4</v>
+      </c>
+      <c r="G85" t="n">
+        <v>18</v>
+      </c>
+      <c r="H85" t="n">
+        <v>9</v>
+      </c>
+      <c r="I85" t="n">
+        <v>207.9</v>
+      </c>
+      <c r="J85" t="n">
+        <v>199.6</v>
+      </c>
+      <c r="K85" t="n">
+        <v>216.2</v>
+      </c>
+      <c r="L85" t="n">
+        <v>318</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L73"/>
+  <autoFilter ref="A1:L85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>